--- a/.claude/skills/bnma/tests/fixtures/prd_fixture.xlsx
+++ b/.claude/skills/bnma/tests/fixtures/prd_fixture.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2422,6 +2422,159 @@
         </is>
       </c>
       <c r="S26" t="inlineStr">
+        <is>
+          <t>fixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260814</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>clamp-test-1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>placebo</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>placebo</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>lilly</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>phase 3</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>36 week</t>
+        </is>
+      </c>
+      <c r="I27">
+        <v>45</v>
+      </c>
+      <c r="J27">
+        <v>100</v>
+      </c>
+      <c r="K27">
+        <v>1.2</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>publication</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>synthetic fixture</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>obese non-t2d</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>mmrm on treatment</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>fixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260814</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>clamp-test-1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>semaglutide 2.4mg qw</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>semaglutide</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>lilly</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>injectable</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>phase 3</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>36 week</t>
+        </is>
+      </c>
+      <c r="I28">
+        <v>45</v>
+      </c>
+      <c r="J28">
+        <v>100</v>
+      </c>
+      <c r="K28">
+        <v>-15</v>
+      </c>
+      <c r="L28">
+        <v>0.5</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>publication</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>synthetic fixture</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>obese non-t2d</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>mmrm on treatment</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
         <is>
           <t>fixture</t>
         </is>

--- a/.claude/skills/bnma/tests/fixtures/prd_fixture.xlsx
+++ b/.claude/skills/bnma/tests/fixtures/prd_fixture.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2575,6 +2575,156 @@
         </is>
       </c>
       <c r="S28" t="inlineStr">
+        <is>
+          <t>fixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260814</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>se-fallback-1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>placebo</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>placebo</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>lilly</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>phase 3</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>36 week</t>
+        </is>
+      </c>
+      <c r="I29">
+        <v>64</v>
+      </c>
+      <c r="J29">
+        <v>100</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>publication</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>synthetic fixture</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>obese non-t2d</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>mmrm on treatment</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>fixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260814</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>se-fallback-1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>hdm2000 5mg qw</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>hdm2000</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>lilly</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>injectable</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>phase 3</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>36 week</t>
+        </is>
+      </c>
+      <c r="I30">
+        <v>64</v>
+      </c>
+      <c r="J30">
+        <v>100</v>
+      </c>
+      <c r="K30">
+        <v>-10</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>publication</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>synthetic fixture</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>obese non-t2d</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>mmrm on treatment</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
         <is>
           <t>fixture</t>
         </is>

--- a/.claude/skills/bnma/tests/fixtures/prd_fixture.xlsx
+++ b/.claude/skills/bnma/tests/fixtures/prd_fixture.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W30"/>
+  <dimension ref="A1:W32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2725,6 +2725,164 @@
         </is>
       </c>
       <c r="S30" t="inlineStr">
+        <is>
+          <t>fixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260814</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>canaflig-vs-canafligizon-1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>canaflig 10mg qw</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>canaflig</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>lilly</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>injectable</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>phase 3</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>36 week</t>
+        </is>
+      </c>
+      <c r="I31">
+        <v>85</v>
+      </c>
+      <c r="J31">
+        <v>100</v>
+      </c>
+      <c r="K31">
+        <v>-12.5</v>
+      </c>
+      <c r="L31">
+        <v>0.6</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>publication</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>synthetic fixture</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>obese non-t2d</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>mmrm on treatment</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>fixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260814</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>canaflig-vs-canafligizon-1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>canafligizon 10mg qw</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>canafligizon</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>lilly</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>injectable</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>phase 3</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>36 week</t>
+        </is>
+      </c>
+      <c r="I32">
+        <v>85</v>
+      </c>
+      <c r="J32">
+        <v>100</v>
+      </c>
+      <c r="K32">
+        <v>-11.8</v>
+      </c>
+      <c r="L32">
+        <v>0.6</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>publication</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>synthetic fixture</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>obese non-t2d</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>mmrm on treatment</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
         <is>
           <t>fixture</t>
         </is>
